--- a/assets/attribute_table.xlsx
+++ b/assets/attribute_table.xlsx
@@ -1,15 +1,857 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr defaultThemeVersion="202300"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GodotProject\PotionProject\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4904856-3396-403C-9C56-01672135F0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-768" yWindow="2184" windowWidth="17916" windowHeight="16176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="属性表" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="275">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>名称</t>
+  </si>
+  <si>
+    <t>分类</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>等级成长</t>
+  </si>
+  <si>
+    <t>词条</t>
+  </si>
+  <si>
+    <t>作用对象</t>
+  </si>
+  <si>
+    <t>可附魔</t>
+  </si>
+  <si>
+    <t>附魔效果</t>
+  </si>
+  <si>
+    <t>buff 数值</t>
+  </si>
+  <si>
+    <t>反应配方</t>
+  </si>
+  <si>
+    <t>实现脚本</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>治疗</t>
+  </si>
+  <si>
+    <t>治疗/生命</t>
+  </si>
+  <si>
+    <t>按目标最大生命百分比回血。回血成功后给目标挂「治疗抵抗」30 秒，期间带治疗属性的物品不再回血（也不会刷新它）。</t>
+  </si>
+  <si>
+    <t>1/2/3 级回 30%/45%/60%；同名两份可升级</t>
+  </si>
+  <si>
+    <t>正面</t>
+  </si>
+  <si>
+    <t>被命中目标</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>治疗+神圣→净化 | 治疗+木质→恢复</t>
+  </si>
+  <si>
+    <t>heal.gd</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>神圣</t>
+  </si>
+  <si>
+    <t>基本属性</t>
+  </si>
+  <si>
+    <t>施加「祝福」：目标受到的回复量提高（治疗、恢复、吸血回血都吃这个加成）。</t>
+  </si>
+  <si>
+    <t>+30%(+10%/级)，持续 8 秒</t>
+  </si>
+  <si>
+    <t>buff=blessing，8.0 秒，标记=[]；healing_received PERCENT_ADD 0.3/+0.1</t>
+  </si>
+  <si>
+    <t>神圣+治疗→净化 | 神圣+恢复→净化 | 神圣+木质→护己 | 神圣+固结→圣佑 | 神圣+风→灵巧 | 神圣+血肉→强身 | 神圣+草本→护己</t>
+  </si>
+  <si>
+    <t>holy.gd</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>恢复</t>
+  </si>
+  <si>
+    <t>立刻回一小口生命，再挂一段按秒回复的恢复 buff。</t>
+  </si>
+  <si>
+    <t>立即回 10% 上限；每跳回复 10(+5/级)</t>
+  </si>
+  <si>
+    <t>buff=regen，6.0 秒，标记=[]；heal_per_tick=10.0 ; heal_per_tick_per_level=5.0</t>
+  </si>
+  <si>
+    <t>恢复+神圣→净化 | 恢复+木质→恢复（等级+1） | 恢复+水→治疗</t>
+  </si>
+  <si>
+    <t>continuous_heal.gd</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>矿物</t>
+  </si>
+  <si>
+    <t>元素/材料</t>
+  </si>
+  <si>
+    <t>挂「护体」增益：提高固定防御（减伤）。</t>
+  </si>
+  <si>
+    <t>开关型（0 级）</t>
+  </si>
+  <si>
+    <t>矿物+木质→固结 | 矿物+火→锋利 | 矿物+防御→防御（等级+1） | 矿物+净化→盐 | 矿物+雷→盐 | 矿物+敏捷→迟缓 | 矿物+锋利→锋利（等级+1） | 矿物+风→盐 | 矿物+血肉→力量 | 矿物+酸→中毒 | 矿物+盐→耐力 | 矿物+草本→防御 | 矿物+冰→滞留</t>
+  </si>
+  <si>
+    <t>mineral.gd</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>木质</t>
+  </si>
+  <si>
+    <t>挂「恢复」增益：按秒回复生命。</t>
+  </si>
+  <si>
+    <t>木质+治疗→恢复 | 木质+神圣→护己 | 木质+恢复→恢复（等级+1） | 木质+矿物→固结 | 木质+固结→固结（等级+1） | 木质+火→火（等级+1） | 木质+强身→强身 | 木质+强身→耐力 | 木质+雷→火 | 木质+水→木质 | 木质+风→敏捷 | 木质+酸→易伤 | 木质+盐→延时 | 木质+草本→荆棘 | 木质+冰→延时</t>
+  </si>
+  <si>
+    <t>woody.gd</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>固结</t>
+  </si>
+  <si>
+    <t>挂「固化」增益：受到的伤害降低。</t>
+  </si>
+  <si>
+    <t>buff=solid，8.0 秒，标记=[]；damage_taken PERCENT_ADD -0.3/+-0.05</t>
+  </si>
+  <si>
+    <t>固结+神圣→圣佑 | 固结+木质→固结（等级+1） | 固结+火→滞留 | 固结+中毒→迟缓 | 固结+迟缓→迟缓（等级+1） | 固结+力量→强身</t>
+  </si>
+  <si>
+    <t>binding.gd</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>爆炸</t>
+  </si>
+  <si>
+    <t>不需要目标：在碎点/命中点引爆，对范围内敌人造成一次爆炸伤害（对玩家伤害很低）。</t>
+  </si>
+  <si>
+    <t>伤害/半径按 √(等级+1) 放大</t>
+  </si>
+  <si>
+    <t>负面</t>
+  </si>
+  <si>
+    <t>命中点/碎点（附魔：被命中目标）</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>不挂 buff（命中直接结算）</t>
+  </si>
+  <si>
+    <t>爆炸+火→爆炸（等级+1） | 爆炸+防御→易伤 | 爆炸+力量→暴怒 | 爆炸+风→爆炸（等级+1） | 爆炸+酸→爆炸 | 爆炸+酸→中毒 | 爆炸+盐→爆炸（等级+1） | 爆炸+冰→裂伤</t>
+  </si>
+  <si>
+    <t>explosive.gd</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>火</t>
+  </si>
+  <si>
+    <t>施加燃烧 DoT；火属性命中时目标还会直接吃到一次火伤害。</t>
+  </si>
+  <si>
+    <t>火伤害 3(+1.5/级)</t>
+  </si>
+  <si>
+    <t>buff=burn，4.0 秒，减益，标记=[]；damage_per_tick=2.0 ; damage_per_tick_per_level=1.0</t>
+  </si>
+  <si>
+    <t>火+矿物→锋利 | 火+木质→火（等级+1） | 火+固结→滞留 | 火+爆炸→爆炸（等级+1） | 火+力量→暴怒 | 火+雷→爆炸 | 火+风→爆炸 | 火+盐→爆炸 | 火+草本→盐 | 火+冰→水</t>
+  </si>
+  <si>
+    <t>fire.gd</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>隐身</t>
+  </si>
+  <si>
+    <t>特殊机制</t>
+  </si>
+  <si>
+    <t>隐身：半透明；怪物无法锁定你。出手/使用道具会显形 3 秒，buff 不消失。</t>
+  </si>
+  <si>
+    <t>buff=invisible，6.0 秒，标记=[&amp;''invisible'']</t>
+  </si>
+  <si>
+    <t>invisibility.gd</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>护己</t>
+  </si>
+  <si>
+    <t>药水级修饰：带护己的药水，正面效果只作用于使用者，负面效果作用于圈内敌方；自喝时负面不结算。</t>
+  </si>
+  <si>
+    <t>中性</t>
+  </si>
+  <si>
+    <t>self_exempt.gd</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>中毒</t>
+  </si>
+  <si>
+    <t>施加中毒 DoT（按秒扣血）。</t>
+  </si>
+  <si>
+    <t>按等级提高跳伤</t>
+  </si>
+  <si>
+    <t>buff=poison，8.0 秒，减益，标记=[]；damage_per_tick=1.0 ; damage_per_tick_per_level=0.5</t>
+  </si>
+  <si>
+    <t>中毒+固结→迟缓 | 中毒+防御→裂伤 | 中毒+力量→虚弱 | 中毒+净化→治疗 | 中毒+强身→易伤 | 中毒+敏捷→迟缓 | 中毒+酸→中毒（等级+1） | 中毒+盐→中毒 | 中毒+盐→虚弱</t>
+  </si>
+  <si>
+    <t>poison.gd</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>迟缓</t>
+  </si>
+  <si>
+    <t>施加减速：降低目标移动速度。</t>
+  </si>
+  <si>
+    <t>按等级提高减速幅度</t>
+  </si>
+  <si>
+    <t>buff=slow，5.0 秒，减益，标记=[]；move_speed PERCENT_ADD -0.35/+-0.1</t>
+  </si>
+  <si>
+    <t>迟缓+固结→迟缓（等级+1） | 迟缓+净化→迅捷 | 迟缓+冰→冰</t>
+  </si>
+  <si>
+    <t>slow.gd</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>迅捷</t>
+  </si>
+  <si>
+    <t>增益/减益</t>
+  </si>
+  <si>
+    <t>施加迅捷：提高移动速度。</t>
+  </si>
+  <si>
+    <t>按等级提高幅度</t>
+  </si>
+  <si>
+    <t>buff=swift，8.0 秒，标记=[]；move_speed PERCENT_ADD 0.3/+0.1</t>
+  </si>
+  <si>
+    <t>迅捷+雷→灵巧 | 迅捷+风→迅捷（等级+1）</t>
+  </si>
+  <si>
+    <t>swift.gd</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>施加防御：提高固定减伤。</t>
+  </si>
+  <si>
+    <t>buff=defense_up，8.0 秒，标记=[]；defense FLAT 1.0/+2.0</t>
+  </si>
+  <si>
+    <t>防御+矿物→防御（等级+1） | 防御+爆炸→易伤 | 防御+中毒→裂伤 | 防御+圣佑→吸收</t>
+  </si>
+  <si>
+    <t>guard.gd</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>力量</t>
+  </si>
+  <si>
+    <t>施加力量：提高造成的伤害（damage_dealt 乘算，武器结算时生效）。</t>
+  </si>
+  <si>
+    <t>buff=sharp，8.0 秒，标记=[]；damage_dealt PERCENT_ADD 0.25/+0.1</t>
+  </si>
+  <si>
+    <t>力量+固结→强身 | 力量+爆炸→暴怒 | 力量+火→暴怒 | 力量+中毒→虚弱</t>
+  </si>
+  <si>
+    <t>powerful.gd</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>净化</t>
+  </si>
+  <si>
+    <t>净化：驱散目标身上所有减益（包括治疗抵抗、冰冻、眩晕）。</t>
+  </si>
+  <si>
+    <t>净化+矿物→盐 | 净化+中毒→治疗 | 净化+迟缓→迅捷 | 净化+虚弱→力量 | 净化+易伤→防御 | 净化+酸→水</t>
+  </si>
+  <si>
+    <t>cleanse.gd</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>荆棘</t>
+  </si>
+  <si>
+    <t>施加荆棘：受到伤害时按比例反弹给攻击者（有反伤链上限）。</t>
+  </si>
+  <si>
+    <t>反弹 35%/级</t>
+  </si>
+  <si>
+    <t>buff=thorns，10.0 秒，标记=[&amp;''thorns'']</t>
+  </si>
+  <si>
+    <t>thorns.gd</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>虚弱</t>
+  </si>
+  <si>
+    <t>施加虚弱：目标出手造成的伤害按百分比降低。</t>
+  </si>
+  <si>
+    <t>按等级提高削减幅度</t>
+  </si>
+  <si>
+    <t>buff=weakness，6.0 秒，减益，标记=[]；damage_dealt PERCENT_ADD -0.3/+-0.1</t>
+  </si>
+  <si>
+    <t>虚弱+净化→力量 | 虚弱+暴怒→虚弱（等级+1） | 虚弱+沉重→虚弱（等级+1）</t>
+  </si>
+  <si>
+    <t>weakness.gd</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>易伤</t>
+  </si>
+  <si>
+    <t>施加易伤：目标受到的伤害增加。</t>
+  </si>
+  <si>
+    <t>+25%(+10%/级)</t>
+  </si>
+  <si>
+    <t>buff=vulnerable，6.0 秒，减益，标记=[]；damage_taken PERCENT_ADD 0.25/+0.1</t>
+  </si>
+  <si>
+    <t>易伤+净化→防御 | 易伤+沉重→易伤（等级+1）</t>
+  </si>
+  <si>
+    <t>vulnerable.gd</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>吸血</t>
+  </si>
+  <si>
+    <t>药水形态：施加吸血 buff，造成伤害按比例回血。附魔形态：命中时直接回复本次伤害的 25%(+10%/级)，不再挂 buff。</t>
+  </si>
+  <si>
+    <t>药水 20%(+5%/级)；附魔 25%(+10%/级)</t>
+  </si>
+  <si>
+    <t>被命中目标（附魔：使用者自己）</t>
+  </si>
+  <si>
+    <t>buff=lifesteal，8.0 秒，标记=[]；lifesteal FLAT 0.2/+0.05</t>
+  </si>
+  <si>
+    <t>lifesteal.gd</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>强身</t>
+  </si>
+  <si>
+    <t>施加强身：临时提高最大生命上限，增加的部分是空血；到期把当前生命压回上限。</t>
+  </si>
+  <si>
+    <t>+3(+1/级)，持续 8 秒</t>
+  </si>
+  <si>
+    <t>buff=fortify，8.0 秒，标记=[]；max_health FLAT 3.0/+1.0</t>
+  </si>
+  <si>
+    <t>强身+木质→强身 | 强身+木质→耐力 | 强身+中毒→易伤 | 强身+冰→隐身 | 强身+圣佑→吸血</t>
+  </si>
+  <si>
+    <t>fortify.gd</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>吸收</t>
+  </si>
+  <si>
+    <t>施加吸收：期间受到的伤害会先正常结算增减伤，再把最终伤害反转成等量回复（4 秒）。</t>
+  </si>
+  <si>
+    <t>buff=absorb，4.0 秒，标记=[&amp;''damage_absorb'']</t>
+  </si>
+  <si>
+    <t>absorb.gd</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>滞留</t>
+  </si>
+  <si>
+    <t>药水级修饰：带滞留的药水破碎后，作用圈会保留一段时间；没有滞留则作用圈时长为 0（落地只结算一次）。</t>
+  </si>
+  <si>
+    <t>2 秒(+1.5/级)</t>
+  </si>
+  <si>
+    <t>linger.gd</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>雷</t>
+  </si>
+  <si>
+    <t>落雷：在目标位置劈下一道雷，对落点半径内的角色造成伤害。作为药水时由作用圈按节拍在圈心落雷；左键使用时原地落雷。</t>
+  </si>
+  <si>
+    <t>5(+2/级)，半径 44，圈节拍 1 秒</t>
+  </si>
+  <si>
+    <t>雷+矿物→盐 | 雷+木质→火 | 雷+火→爆炸 | 雷+迅捷→灵巧 | 雷+水→雷（等级+1） | 雷+风→迅捷 | 雷+盐→灵巧 | 雷+草本→火 | 雷+冰→急速</t>
+  </si>
+  <si>
+    <t>thunder.gd</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>暴怒</t>
+  </si>
+  <si>
+    <t>施加暴怒：提高出手暴击率。</t>
+  </si>
+  <si>
+    <t>+10%(+4%/级)</t>
+  </si>
+  <si>
+    <t>buff=rage，8.0 秒，标记=[]；crit_chance FLAT 0.1/+0.04</t>
+  </si>
+  <si>
+    <t>暴怒+虚弱→虚弱（等级+1）</t>
+  </si>
+  <si>
+    <t>rage.gd</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>敏捷</t>
+  </si>
+  <si>
+    <t>施加敏捷：提高出手速度（前摇/持续/后摇一起加快）。</t>
+  </si>
+  <si>
+    <t>+20%(+8%/级)</t>
+  </si>
+  <si>
+    <t>buff=agility，8.0 秒，标记=[]；attack_speed FLAT 0.2/+0.08</t>
+  </si>
+  <si>
+    <t>敏捷+矿物→迟缓 | 敏捷+中毒→迟缓 | 敏捷+风→急速</t>
+  </si>
+  <si>
+    <t>agility.gd</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>灵巧</t>
+  </si>
+  <si>
+    <t>施加灵巧：加快闪避次数的充能速度。</t>
+  </si>
+  <si>
+    <t>+35%(+15%/级)</t>
+  </si>
+  <si>
+    <t>buff=deftness，8.0 秒，标记=[]；dodge_recovery FLAT 0.35/+0.15</t>
+  </si>
+  <si>
+    <t>灵巧+耐力→灵巧（等级+1）</t>
+  </si>
+  <si>
+    <t>deftness.gd</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>锋利</t>
+  </si>
+  <si>
+    <t>附魔专用</t>
+  </si>
+  <si>
+    <t>附到武器上后，武器伤害直接提高（不挂 buff）。</t>
+  </si>
+  <si>
+    <t>+3(+1.5/级)</t>
+  </si>
+  <si>
+    <t>直接加在武器伤害上</t>
+  </si>
+  <si>
+    <t>锋利+矿物→锋利（等级+1） | 锋利+沉重→裂伤</t>
+  </si>
+  <si>
+    <t>sharpness.gd</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>急速</t>
+  </si>
+  <si>
+    <t>附到武器上后，武器出手速度直接提高（不挂 buff），前摇/持续/后摇与收招硬直一起加快。</t>
+  </si>
+  <si>
+    <t>直接加在武器攻速上</t>
+  </si>
+  <si>
+    <t>haste.gd</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>裂伤</t>
+  </si>
+  <si>
+    <t>命中时对被命中的目标追加一次固定伤害。</t>
+  </si>
+  <si>
+    <t>2(+1.5/级)</t>
+  </si>
+  <si>
+    <t>命中追加伤害</t>
+  </si>
+  <si>
+    <t>rend.gd</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>水</t>
+  </si>
+  <si>
+    <t>本身没有实际效果，是后续合成新属性的底料。</t>
+  </si>
+  <si>
+    <t>不可升级（0 级）</t>
+  </si>
+  <si>
+    <t>水+恢复→治疗 | 水+木质→木质 | 水+雷→雷（等级+1） | 水+酸→中毒 | 水+盐→净化 | 水+草本→治疗 | 水+冰→冰</t>
+  </si>
+  <si>
+    <t>water.gd</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>风</t>
+  </si>
+  <si>
+    <t>风+神圣→灵巧 | 风+矿物→盐 | 风+木质→敏捷 | 风+爆炸→爆炸（等级+1） | 风+火→爆炸 | 风+迅捷→迅捷（等级+1） | 风+雷→迅捷 | 风+敏捷→急速 | 风+冰→迟缓</t>
+  </si>
+  <si>
+    <t>wind.gd</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>血肉</t>
+  </si>
+  <si>
+    <t>血肉+神圣→强身 | 血肉+矿物→力量 | 血肉+酸→中毒 | 血肉+草本→恢复 | 血肉+冰→敏捷</t>
+  </si>
+  <si>
+    <t>flesh.gd</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>酸</t>
+  </si>
+  <si>
+    <t>酸+矿物→中毒 | 酸+木质→易伤 | 酸+爆炸→爆炸 | 酸+爆炸→中毒 | 酸+中毒→中毒（等级+1） | 酸+净化→水 | 酸+水→中毒 | 酸+血肉→中毒 | 酸+盐→中毒 | 酸+草本→迟缓</t>
+  </si>
+  <si>
+    <t>acid.gd</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>盐</t>
+  </si>
+  <si>
+    <t>盐+矿物→耐力 | 盐+木质→延时 | 盐+爆炸→爆炸（等级+1） | 盐+火→爆炸 | 盐+中毒→中毒 | 盐+中毒→虚弱 | 盐+雷→灵巧 | 盐+水→净化 | 盐+酸→中毒 | 盐+草本→力量 | 盐+冰→水</t>
+  </si>
+  <si>
+    <t>salt.gd</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>草本</t>
+  </si>
+  <si>
+    <t>本身没有实际效果，是后续合成新属性的底料（草本类）。</t>
+  </si>
+  <si>
+    <t>草本+神圣→护己 | 草本+矿物→防御 | 草本+木质→荆棘 | 草本+火→盐 | 草本+雷→火 | 草本+水→治疗 | 草本+血肉→恢复 | 草本+酸→迟缓 | 草本+盐→力量 | 草本+冰→滞留</t>
+  </si>
+  <si>
+    <t>herbal.gd</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>冰</t>
+  </si>
+  <si>
+    <t>给目标积累冰冻值（记在目标身上）；攒满 4 点后清零、造成一次伤害并冻结目标（硬控，不能移动/出手）。</t>
+  </si>
+  <si>
+    <t>每层 1(+0.5/级)，触发伤害 4(+2/级)</t>
+  </si>
+  <si>
+    <t>命中时积累冰冻值</t>
+  </si>
+  <si>
+    <t>冰冻值攒满时挂 frozen（1.5 秒，硬控）</t>
+  </si>
+  <si>
+    <t>冰+矿物→滞留 | 冰+木质→延时 | 冰+爆炸→裂伤 | 冰+火→水 | 冰+迟缓→冰 | 冰+强身→隐身 | 冰+雷→急速 | 冰+水→冰 | 冰+风→迟缓 | 冰+血肉→敏捷 | 冰+盐→水 | 冰+草本→滞留</t>
+  </si>
+  <si>
+    <t>ice.gd</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>沉重</t>
+  </si>
+  <si>
+    <t>命中时按概率把目标砸晕（眩晕 = 硬控，不能移动/出手）。</t>
+  </si>
+  <si>
+    <t>概率 25%(+10%/级)</t>
+  </si>
+  <si>
+    <t>命中时概率眩晕目标</t>
+  </si>
+  <si>
+    <t>命中概率挂 stun（1 秒，硬控）</t>
+  </si>
+  <si>
+    <t>沉重+虚弱→虚弱（等级+1） | 沉重+易伤→易伤（等级+1） | 沉重+锋利→裂伤</t>
+  </si>
+  <si>
+    <t>heavy.gd</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>圣佑</t>
+  </si>
+  <si>
+    <t>施加「圣佑」：受到的伤害降低并缓慢回复，最高 3 级逐级提升。</t>
+  </si>
+  <si>
+    <t>-25%(-5%/级) 受伤；每跳回复 0.5(+0.25/级)</t>
+  </si>
+  <si>
+    <t>buff=holy，6.0 秒，标记=[]；damage_taken PERCENT_ADD -0.25/+-0.05；heal_per_tick=0.5 ; heal_per_tick_per_level=0.25</t>
+  </si>
+  <si>
+    <t>圣佑+防御→吸收 | 圣佑+强身→吸血</t>
+  </si>
+  <si>
+    <t>sanctuary.gd</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>延时</t>
+  </si>
+  <si>
+    <t>药水级修饰：让同一瓶药水里其它带持续时间的效果更久（施加的 buff 时长、作用圈留存时长都按倍率放大）。</t>
+  </si>
+  <si>
+    <t>1.5 倍(+0.25/级)</t>
+  </si>
+  <si>
+    <t>extend.gd</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>耐力</t>
+  </si>
+  <si>
+    <t>施加「耐力」：闪避次数上限 +1，多出来的次数立刻可用。</t>
+  </si>
+  <si>
+    <t>+1(+1/级)，持续 8 秒</t>
+  </si>
+  <si>
+    <t>buff=stamina，8.0 秒，标记=[]；dodge_max_charges FLAT 1.0/+1.0</t>
+  </si>
+  <si>
+    <t>耐力+灵巧→灵巧（等级+1）</t>
+  </si>
+  <si>
+    <t>stamina.gd</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="微软雅黑"/>
@@ -19,15 +861,17 @@
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1F3B57"/>
-      <name val="微软雅黑"/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -37,12 +881,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F4F6F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F6FA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -84,9 +922,334 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="0E2841"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E8E8E8"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="156082"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="E97132"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="196B24"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="0F9ED5"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="A02B93"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="4EA72E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="467886"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="96607D"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -222,7 +1385,7 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+神圣→净化 | 治疗+木质→恢复</t>
+          <t xml:space="preserve">治疗+神圣→净化 | 治疗+木质→恢复 | 治疗+中毒→抵消 | 治疗+风→迅捷 | 治疗+血肉→力量 | 治疗+盐→护己 | 治疗+草本→恢复 | 治疗+冰→灵巧 | 治疗+治疗→治疗（等级+1）</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
@@ -284,7 +1447,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">神圣+治疗→净化 | 神圣+恢复→净化 | 神圣+木质→护己 | 神圣+固结→圣佑 | 神圣+风→灵巧 | 神圣+血肉→强身 | 神圣+草本→护己</t>
+          <t xml:space="preserve">治疗+神圣→净化 | 神圣+恢复→净化 | 神圣+木质→护己 | 神圣+固结→圣佑 | 神圣+风→灵巧 | 神圣+血肉→强身</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -346,7 +1509,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">恢复+神圣→净化 | 恢复+木质→恢复（等级+1） | 恢复+水→治疗</t>
+          <t xml:space="preserve">神圣+恢复→净化 | 恢复+木质→恢复（等级+1） | 恢复+中毒→抵消 | 恢复+水→治疗 | 恢复+风→敏捷 | 恢复+盐→滞留 | 恢复+恢复→恢复（等级+1）</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -408,7 +1571,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+木质→固结 | 矿物+火→锋利 | 矿物+防御→防御（等级+1） | 矿物+净化→盐 | 矿物+雷→盐 | 矿物+敏捷→迟缓 | 矿物+锋利→锋利（等级+1） | 矿物+风→盐 | 矿物+血肉→力量 | 矿物+酸→中毒 | 矿物+盐→耐力 | 矿物+草本→防御 | 矿物+冰→滞留</t>
+          <t xml:space="preserve">矿物+木质→固结 | 矿物+火→锋利 | 矿物+迟缓→沉重 | 矿物+防御→防御（等级+1） | 矿物+净化→盐 | 矿物+敏捷→迟缓 | 矿物+锋利→锋利（等级+1） | 矿物+风→盐 | 矿物+血肉→力量 | 矿物+酸→中毒 | 矿物+盐→耐力 | 矿物+草本→防御 | 矿物+矿物→沉重</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -470,7 +1633,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">木质+治疗→恢复 | 木质+神圣→护己 | 木质+恢复→恢复（等级+1） | 木质+矿物→固结 | 木质+固结→固结（等级+1） | 木质+火→火（等级+1） | 木质+强身→强身 | 木质+强身→耐力 | 木质+雷→火 | 木质+水→木质 | 木质+风→敏捷 | 木质+酸→易伤 | 木质+盐→延时 | 木质+草本→荆棘 | 木质+冰→延时</t>
+          <t xml:space="preserve">治疗+木质→恢复 | 神圣+木质→护己 | 恢复+木质→恢复（等级+1） | 矿物+木质→固结 | 木质+固结→固结（等级+1） | 木质+火→火（等级+1） | 木质+强身→强身+耐力 | 木质+雷→火 | 木质+风→敏捷 | 木质+酸→迟缓 | 木质+盐→延时 | 木质+草本→荆棘 | 木质+冰→延时</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -532,7 +1695,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">固结+神圣→圣佑 | 固结+木质→固结（等级+1） | 固结+火→滞留 | 固结+中毒→迟缓 | 固结+迟缓→迟缓（等级+1） | 固结+力量→强身</t>
+          <t xml:space="preserve">神圣+固结→圣佑 | 木质+固结→固结（等级+1） | 固结+火→滞留 | 固结+中毒→迟缓 | 固结+迟缓→迟缓（等级+1） | 固结+力量→强身 | 固结+水→冰 | 固结+风→迟缓 | 固结+盐→耐力</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -594,7 +1757,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">爆炸+火→爆炸（等级+1） | 爆炸+防御→易伤 | 爆炸+力量→暴怒 | 爆炸+风→爆炸（等级+1） | 爆炸+酸→爆炸 | 爆炸+酸→中毒 | 爆炸+盐→爆炸（等级+1） | 爆炸+冰→裂伤</t>
+          <t xml:space="preserve">爆炸+火→爆炸（等级+1） | 爆炸+防御→易伤 | 爆炸+力量→暴怒 | 爆炸+荆棘→裂伤 | 爆炸+风→爆炸（等级+1） | 爆炸+酸→爆炸+中毒 | 爆炸+盐→爆炸（等级+1） | 爆炸+冰→裂伤 | 爆炸+爆炸→爆炸（等级+1）</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -656,7 +1819,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">火+矿物→锋利 | 火+木质→火（等级+1） | 火+固结→滞留 | 火+爆炸→爆炸（等级+1） | 火+力量→暴怒 | 火+雷→爆炸 | 火+风→爆炸 | 火+盐→爆炸 | 火+草本→盐 | 火+冰→水</t>
+          <t xml:space="preserve">矿物+火→锋利 | 木质+火→火（等级+1） | 固结+火→滞留 | 爆炸+火→爆炸（等级+1） | 火+力量→暴怒 | 火+雷→爆炸 | 火+水→抵消 | 火+风→爆炸 | 火+血肉→恢复 | 火+盐→爆炸 | 火+草本→盐 | 火+冰→水 | 火+火→火（等级+1）</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -713,7 +1876,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=invisible，6.0 秒，标记=[&amp;''invisible'']</t>
+          <t xml:space="preserve">buff=invisible，6.0 秒，标记=[&amp;amp;''invisible'']</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -842,7 +2005,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">中毒+固结→迟缓 | 中毒+防御→裂伤 | 中毒+力量→虚弱 | 中毒+净化→治疗 | 中毒+强身→易伤 | 中毒+敏捷→迟缓 | 中毒+酸→中毒（等级+1） | 中毒+盐→中毒 | 中毒+盐→虚弱</t>
+          <t xml:space="preserve">治疗+中毒→抵消 | 恢复+中毒→抵消 | 固结+中毒→迟缓 | 中毒+防御→裂伤 | 中毒+力量→虚弱 | 中毒+净化→治疗 | 中毒+强身→易伤 | 中毒+敏捷→迟缓 | 中毒+水→中毒（等级-1） | 中毒+盐→中毒+虚弱 | 中毒+中毒→中毒（等级+1）</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
@@ -904,7 +2067,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迟缓+固结→迟缓（等级+1） | 迟缓+净化→迅捷 | 迟缓+冰→冰</t>
+          <t xml:space="preserve">矿物+迟缓→沉重 | 固结+迟缓→迟缓（等级+1） | 迟缓+迅捷→抵消 | 迟缓+净化→迅捷 | 迟缓+冰→冰 | 迟缓+迟缓→迟缓（等级+1）</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -966,7 +2129,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迅捷+雷→灵巧 | 迅捷+风→迅捷（等级+1）</t>
+          <t xml:space="preserve">迟缓+迅捷→抵消 | 迅捷+雷→灵巧 | 迅捷+风→迅捷（等级+1） | 迅捷+迅捷→迅捷（等级+1）</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1028,7 +2191,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">防御+矿物→防御（等级+1） | 防御+爆炸→易伤 | 防御+中毒→裂伤 | 防御+圣佑→吸收</t>
+          <t xml:space="preserve">矿物+防御→防御（等级+1） | 爆炸+防御→易伤 | 中毒+防御→裂伤 | 防御+酸→抵消 | 防御+圣佑→吸收 | 防御+防御→防御（等级+1）</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1090,7 +2253,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">力量+固结→强身 | 力量+爆炸→暴怒 | 力量+火→暴怒 | 力量+中毒→虚弱</t>
+          <t xml:space="preserve">固结+力量→强身 | 爆炸+力量→暴怒 | 火+力量→暴怒 | 中毒+力量→虚弱 | 力量+虚弱→抵消</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1152,7 +2315,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">净化+矿物→盐 | 净化+中毒→治疗 | 净化+迟缓→迅捷 | 净化+虚弱→力量 | 净化+易伤→防御 | 净化+酸→水</t>
+          <t xml:space="preserve">矿物+净化→盐 | 中毒+净化→治疗 | 迟缓+净化→迅捷 | 净化+虚弱→力量 | 净化+易伤→防御 | 净化+酸→水</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1209,12 +2372,12 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=thorns，10.0 秒，标记=[&amp;''thorns'']</t>
+          <t xml:space="preserve">buff=thorns，10.0 秒，标记=[&amp;amp;''thorns'']</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">爆炸+荆棘→裂伤 | 荆棘+荆棘→荆棘（等级+1）</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1276,7 +2439,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">虚弱+净化→力量 | 虚弱+暴怒→虚弱（等级+1） | 虚弱+沉重→虚弱（等级+1）</t>
+          <t xml:space="preserve">力量+虚弱→抵消 | 净化+虚弱→力量 | 虚弱+暴怒→虚弱（等级+1） | 虚弱+沉重→虚弱（等级+1） | 虚弱+虚弱→虚弱（等级+1）</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1338,7 +2501,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">易伤+净化→防御 | 易伤+沉重→易伤（等级+1）</t>
+          <t xml:space="preserve">净化+易伤→防御 | 易伤+沉重→易伤（等级+1）</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1400,7 +2563,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">吸血+吸血→吸血（等级+1）</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1462,7 +2625,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">强身+木质→强身 | 强身+木质→耐力 | 强身+中毒→易伤 | 强身+冰→隐身 | 强身+圣佑→吸血</t>
+          <t xml:space="preserve">木质+强身→强身+耐力 | 中毒+强身→易伤 | 强身+冰→隐身 | 强身+圣佑→吸血 | 强身+强身→强身（等级+1）</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -1519,7 +2682,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=absorb，4.0 秒，标记=[&amp;''damage_absorb'']</t>
+          <t xml:space="preserve">buff=absorb，4.0 秒，标记=[&amp;amp;''damage_absorb'']</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1586,7 +2749,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">滞留+滞留→滞留（等级+1）</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -1648,7 +2811,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">雷+矿物→盐 | 雷+木质→火 | 雷+火→爆炸 | 雷+迅捷→灵巧 | 雷+水→雷（等级+1） | 雷+风→迅捷 | 雷+盐→灵巧 | 雷+草本→火 | 雷+冰→急速</t>
+          <t xml:space="preserve">木质+雷→火 | 火+雷→爆炸 | 迅捷+雷→灵巧 | 雷+水→雷（等级+1） | 雷+风→迅捷 | 雷+盐→灵巧 | 雷+草本→火 | 雷+冰→急速 | 雷+雷→雷（等级+1）</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -1710,7 +2873,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">暴怒+虚弱→虚弱（等级+1）</t>
+          <t xml:space="preserve">虚弱+暴怒→虚弱（等级+1）</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -1772,7 +2935,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">敏捷+矿物→迟缓 | 敏捷+中毒→迟缓 | 敏捷+风→急速</t>
+          <t xml:space="preserve">矿物+敏捷→迟缓 | 中毒+敏捷→迟缓 | 敏捷+风→急速 | 敏捷+敏捷→敏捷（等级+1）</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -1834,7 +2997,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">灵巧+耐力→灵巧（等级+1）</t>
+          <t xml:space="preserve">灵巧+耐力→灵巧（等级+1） | 灵巧+灵巧→灵巧（等级+1）</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -1896,7 +3059,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">锋利+矿物→锋利（等级+1） | 锋利+沉重→裂伤</t>
+          <t xml:space="preserve">矿物+锋利→锋利（等级+1） | 锋利+沉重→裂伤 | 锋利+锋利→锋利（等级+1）</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -1958,7 +3121,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">急速+急速→急速（等级+1）</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -2020,7 +3183,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">裂伤+裂伤→裂伤（等级+1）</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
@@ -2082,7 +3245,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">水+恢复→治疗 | 水+木质→木质 | 水+雷→雷（等级+1） | 水+酸→中毒 | 水+盐→净化 | 水+草本→治疗 | 水+冰→冰</t>
+          <t xml:space="preserve">恢复+水→治疗 | 固结+水→冰 | 火+水→抵消 | 中毒+水→中毒（等级-1） | 雷+水→雷（等级+1） | 水+酸→中毒 | 水+盐→净化 | 水+草本→治疗 | 水+冰→冰</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2144,7 +3307,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">风+神圣→灵巧 | 风+矿物→盐 | 风+木质→敏捷 | 风+爆炸→爆炸（等级+1） | 风+火→爆炸 | 风+迅捷→迅捷（等级+1） | 风+雷→迅捷 | 风+敏捷→急速 | 风+冰→迟缓</t>
+          <t xml:space="preserve">治疗+风→迅捷 | 神圣+风→灵巧 | 恢复+风→敏捷 | 矿物+风→盐 | 木质+风→敏捷 | 固结+风→迟缓 | 爆炸+风→爆炸（等级+1） | 火+风→爆炸 | 迅捷+风→迅捷（等级+1） | 雷+风→迅捷 | 敏捷+风→急速 | 风+冰→迟缓 | 风+风→迅捷</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2206,7 +3369,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">血肉+神圣→强身 | 血肉+矿物→力量 | 血肉+酸→中毒 | 血肉+草本→恢复 | 血肉+冰→敏捷</t>
+          <t xml:space="preserve">治疗+血肉→力量 | 神圣+血肉→强身 | 矿物+血肉→力量 | 火+血肉→恢复 | 血肉+酸→中毒 | 血肉+草本→恢复 | 血肉+冰→敏捷</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2268,7 +3431,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">酸+矿物→中毒 | 酸+木质→易伤 | 酸+爆炸→爆炸 | 酸+爆炸→中毒 | 酸+中毒→中毒（等级+1） | 酸+净化→水 | 酸+水→中毒 | 酸+血肉→中毒 | 酸+盐→中毒 | 酸+草本→迟缓</t>
+          <t xml:space="preserve">矿物+酸→中毒 | 木质+酸→迟缓 | 爆炸+酸→爆炸+中毒 | 防御+酸→抵消 | 净化+酸→水 | 水+酸→中毒 | 血肉+酸→中毒 | 酸+盐→中毒</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2330,7 +3493,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">盐+矿物→耐力 | 盐+木质→延时 | 盐+爆炸→爆炸（等级+1） | 盐+火→爆炸 | 盐+中毒→中毒 | 盐+中毒→虚弱 | 盐+雷→灵巧 | 盐+水→净化 | 盐+酸→中毒 | 盐+草本→力量 | 盐+冰→水</t>
+          <t xml:space="preserve">治疗+盐→护己 | 恢复+盐→滞留 | 矿物+盐→耐力 | 木质+盐→延时 | 固结+盐→耐力 | 爆炸+盐→爆炸（等级+1） | 火+盐→爆炸 | 中毒+盐→中毒+虚弱 | 雷+盐→灵巧 | 水+盐→净化 | 酸+盐→中毒 | 盐+草本→力量 | 盐+冰→滞留</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2392,7 +3555,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">草本+神圣→护己 | 草本+矿物→防御 | 草本+木质→荆棘 | 草本+火→盐 | 草本+雷→火 | 草本+水→治疗 | 草本+血肉→恢复 | 草本+酸→迟缓 | 草本+盐→力量 | 草本+冰→滞留</t>
+          <t xml:space="preserve">治疗+草本→恢复 | 矿物+草本→防御 | 木质+草本→荆棘 | 火+草本→盐 | 雷+草本→火 | 水+草本→治疗 | 血肉+草本→恢复 | 盐+草本→力量 | 草本+冰→滞留</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -2454,7 +3617,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">冰+矿物→滞留 | 冰+木质→延时 | 冰+爆炸→裂伤 | 冰+火→水 | 冰+迟缓→冰 | 冰+强身→隐身 | 冰+雷→急速 | 冰+水→冰 | 冰+风→迟缓 | 冰+血肉→敏捷 | 冰+盐→水 | 冰+草本→滞留</t>
+          <t xml:space="preserve">治疗+冰→灵巧 | 木质+冰→延时 | 爆炸+冰→裂伤 | 火+冰→水 | 迟缓+冰→冰 | 强身+冰→隐身 | 雷+冰→急速 | 水+冰→冰 | 风+冰→迟缓 | 血肉+冰→敏捷 | 盐+冰→滞留 | 草本+冰→滞留 | 冰+冰→冰（等级+1）</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
@@ -2516,7 +3679,7 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">沉重+虚弱→虚弱（等级+1） | 沉重+易伤→易伤（等级+1） | 沉重+锋利→裂伤</t>
+          <t xml:space="preserve">虚弱+沉重→虚弱（等级+1） | 易伤+沉重→易伤（等级+1） | 锋利+沉重→裂伤 | 沉重+沉重→沉重（等级+1）</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
@@ -2578,7 +3741,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">圣佑+防御→吸收 | 圣佑+强身→吸血</t>
+          <t xml:space="preserve">防御+圣佑→吸收 | 强身+圣佑→吸血 | 圣佑+圣佑→圣佑（等级+1）</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -2640,7 +3803,7 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">延时+延时→延时（等级+1）</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
@@ -2702,7 +3865,7 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">耐力+灵巧→灵巧（等级+1）</t>
+          <t xml:space="preserve">灵巧+耐力→灵巧（等级+1） | 耐力+耐力→耐力（等级+1）</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">

--- a/assets/attribute_table.xlsx
+++ b/assets/attribute_table.xlsx
@@ -1447,7 +1447,7 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+神圣→净化 | 神圣+恢复→净化 | 神圣+木质→护己 | 神圣+固结→圣佑 | 神圣+风→灵巧 | 神圣+血肉→强身</t>
+          <t xml:space="preserve">治疗+神圣→净化 | 神圣+恢复→净化 | 神圣+固结→圣佑 | 神圣+防御→圣佑 | 神圣+风→灵巧 | 神圣+血肉→护己 | 神圣+酸→易伤</t>
         </is>
       </c>
       <c r="L3" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">神圣+恢复→净化 | 恢复+木质→恢复（等级+1） | 恢复+中毒→抵消 | 恢复+水→治疗 | 恢复+风→敏捷 | 恢复+盐→滞留 | 恢复+恢复→恢复（等级+1）</t>
+          <t xml:space="preserve">神圣+恢复→净化 | 恢复+木质→恢复（等级+1） | 恢复+中毒→抵消 | 恢复+水→治疗 | 恢复+风→敏捷 | 恢复+血肉→强身 | 恢复+盐→滞留 | 恢复+恢复→恢复（等级+1）</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+木质→固结 | 矿物+火→锋利 | 矿物+迟缓→沉重 | 矿物+防御→防御（等级+1） | 矿物+净化→盐 | 矿物+敏捷→迟缓 | 矿物+锋利→锋利（等级+1） | 矿物+风→盐 | 矿物+血肉→力量 | 矿物+酸→中毒 | 矿物+盐→耐力 | 矿物+草本→防御 | 矿物+矿物→沉重</t>
+          <t xml:space="preserve">矿物+木质→固结 | 矿物+火→锋利 | 矿物+迟缓→沉重 | 矿物+净化→盐 | 矿物+敏捷→迟缓 | 矿物+锋利→锋利（等级+1） | 矿物+风→盐 | 矿物+血肉→力量 | 矿物+酸→中毒 | 矿物+盐→耐力 | 矿物+草本→防御 | 矿物+矿物→沉重</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -1633,7 +1633,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+木质→恢复 | 神圣+木质→护己 | 恢复+木质→恢复（等级+1） | 矿物+木质→固结 | 木质+固结→固结（等级+1） | 木质+火→火（等级+1） | 木质+强身→强身+耐力 | 木质+雷→火 | 木质+风→敏捷 | 木质+酸→迟缓 | 木质+盐→延时 | 木质+草本→荆棘 | 木质+冰→延时</t>
+          <t xml:space="preserve">治疗+木质→恢复 | 恢复+木质→恢复（等级+1） | 矿物+木质→固结 | 木质+火→火（等级+1） | 木质+强身→强身+耐力 | 木质+雷→火 | 木质+风→敏捷 | 木质+血肉→虚弱 | 木质+酸→迟缓 | 木质+盐→延时 | 木质+草本→荆棘 | 木质+冰→延时</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">神圣+固结→圣佑 | 木质+固结→固结（等级+1） | 固结+火→滞留 | 固结+中毒→迟缓 | 固结+迟缓→迟缓（等级+1） | 固结+力量→强身 | 固结+水→冰 | 固结+风→迟缓 | 固结+盐→耐力</t>
+          <t xml:space="preserve">神圣+固结→圣佑 | 固结+火→滞留 | 固结+中毒→迟缓 | 固结+迟缓→迟缓（等级+1） | 固结+力量→强身 | 固结+水→冰 | 固结+风→迟缓 | 固结+盐→耐力</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+火→锋利 | 木质+火→火（等级+1） | 固结+火→滞留 | 爆炸+火→爆炸（等级+1） | 火+力量→暴怒 | 火+雷→爆炸 | 火+水→抵消 | 火+风→爆炸 | 火+血肉→恢复 | 火+盐→爆炸 | 火+草本→盐 | 火+冰→水 | 火+火→火（等级+1）</t>
+          <t xml:space="preserve">矿物+火→锋利 | 木质+火→火（等级+1） | 固结+火→滞留 | 爆炸+火→爆炸（等级+1） | 火+力量→暴怒 | 火+雷→爆炸 | 火+水→抵消 | 火+风→爆炸 | 火+血肉→恢复 | 火+酸→力量 | 火+盐→爆炸 | 火+草本→盐 | 火+冰→水 | 火+火→火（等级+1）</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=invisible，6.0 秒，标记=[&amp;amp;''invisible'']</t>
+          <t xml:space="preserve">buff=invisible，6.0 秒，标记=[&amp;''invisible'']</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">迟缓+迅捷→抵消 | 迅捷+雷→灵巧 | 迅捷+风→迅捷（等级+1） | 迅捷+迅捷→迅捷（等级+1）</t>
+          <t xml:space="preserve">迟缓+迅捷→抵消 | 迅捷+雷→灵巧 | 迅捷+风→迅捷（等级+1） | 迅捷+酸→急速 | 迅捷+迅捷→迅捷（等级+1）</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+防御→防御（等级+1） | 爆炸+防御→易伤 | 中毒+防御→裂伤 | 防御+酸→抵消 | 防御+圣佑→吸收 | 防御+防御→防御（等级+1）</t>
+          <t xml:space="preserve">神圣+防御→圣佑 | 爆炸+防御→易伤 | 中毒+防御→裂伤 | 防御+酸→抵消 | 防御+圣佑→吸收 | 防御+防御→防御（等级+1）</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=thorns，10.0 秒，标记=[&amp;amp;''thorns'']</t>
+          <t xml:space="preserve">buff=thorns，10.0 秒，标记=[&amp;''thorns'']</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">buff=absorb，4.0 秒，标记=[&amp;amp;''damage_absorb'']</t>
+          <t xml:space="preserve">buff=absorb，4.0 秒，标记=[&amp;''damage_absorb'']</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">木质+雷→火 | 火+雷→爆炸 | 迅捷+雷→灵巧 | 雷+水→雷（等级+1） | 雷+风→迅捷 | 雷+盐→灵巧 | 雷+草本→火 | 雷+冰→急速 | 雷+雷→雷（等级+1）</t>
+          <t xml:space="preserve">木质+雷→火 | 火+雷→爆炸 | 迅捷+雷→灵巧 | 雷+水→雷（等级+1） | 雷+风→迅捷 | 雷+血肉→暴怒 | 雷+酸→暴怒 | 雷+盐→灵巧 | 雷+草本→火 | 雷+冰→急速 | 雷+雷→雷（等级+1）</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+锋利→锋利（等级+1） | 锋利+沉重→裂伤 | 锋利+锋利→锋利（等级+1）</t>
+          <t xml:space="preserve">矿物+锋利→锋利（等级+1） | 锋利+酸→虚弱 | 锋利+沉重→裂伤 | 锋利+锋利→锋利（等级+1）</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+风→迅捷 | 神圣+风→灵巧 | 恢复+风→敏捷 | 矿物+风→盐 | 木质+风→敏捷 | 固结+风→迟缓 | 爆炸+风→爆炸（等级+1） | 火+风→爆炸 | 迅捷+风→迅捷（等级+1） | 雷+风→迅捷 | 敏捷+风→急速 | 风+冰→迟缓 | 风+风→迅捷</t>
+          <t xml:space="preserve">治疗+风→迅捷 | 神圣+风→灵巧 | 恢复+风→敏捷 | 矿物+风→盐 | 木质+风→敏捷 | 固结+风→迟缓 | 爆炸+风→爆炸（等级+1） | 火+风→爆炸 | 迅捷+风→迅捷（等级+1） | 雷+风→迅捷 | 敏捷+风→急速 | 风+酸→敏捷 | 风+盐→灵巧 | 风+冰→迟缓 | 风+风→迅捷</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+血肉→力量 | 神圣+血肉→强身 | 矿物+血肉→力量 | 火+血肉→恢复 | 血肉+酸→中毒 | 血肉+草本→恢复 | 血肉+冰→敏捷</t>
+          <t xml:space="preserve">治疗+血肉→力量 | 神圣+血肉→护己 | 恢复+血肉→强身 | 矿物+血肉→力量 | 木质+血肉→虚弱 | 火+血肉→恢复 | 雷+血肉→暴怒 | 血肉+酸→中毒 | 血肉+盐→延时 | 血肉+草本→恢复 | 血肉+冰→敏捷</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">矿物+酸→中毒 | 木质+酸→迟缓 | 爆炸+酸→爆炸+中毒 | 防御+酸→抵消 | 净化+酸→水 | 水+酸→中毒 | 血肉+酸→中毒 | 酸+盐→中毒</t>
+          <t xml:space="preserve">神圣+酸→易伤 | 矿物+酸→中毒 | 木质+酸→迟缓 | 爆炸+酸→爆炸+中毒 | 火+酸→力量 | 迅捷+酸→急速 | 防御+酸→抵消 | 净化+酸→水 | 雷+酸→暴怒 | 锋利+酸→虚弱 | 水+酸→中毒 | 风+酸→敏捷 | 血肉+酸→中毒 | 酸+盐→中毒</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -3493,7 +3493,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">治疗+盐→护己 | 恢复+盐→滞留 | 矿物+盐→耐力 | 木质+盐→延时 | 固结+盐→耐力 | 爆炸+盐→爆炸（等级+1） | 火+盐→爆炸 | 中毒+盐→中毒+虚弱 | 雷+盐→灵巧 | 水+盐→净化 | 酸+盐→中毒 | 盐+草本→力量 | 盐+冰→滞留</t>
+          <t xml:space="preserve">治疗+盐→护己 | 恢复+盐→滞留 | 矿物+盐→耐力 | 木质+盐→延时 | 固结+盐→耐力 | 爆炸+盐→爆炸（等级+1） | 火+盐→爆炸 | 中毒+盐→中毒+虚弱 | 雷+盐→灵巧 | 水+盐→净化 | 风+盐→灵巧 | 血肉+盐→延时 | 酸+盐→中毒 | 盐+草本→力量 | 盐+冰→滞留</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
